--- a/data/trans_camb/P16A04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,19</t>
+          <t>-1,74; 1,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,17</t>
+          <t>-2,98; 0,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,67</t>
+          <t>-1,97; 3,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,21</t>
+          <t>-0,1; 3,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,02</t>
+          <t>-0,82; 3,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,83</t>
+          <t>-1,01; 4,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,5</t>
+          <t>-0,25; 2,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,0</t>
+          <t>-1,37; 0,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,75</t>
+          <t>-1,05; 2,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 234,68</t>
+          <t>-68,43; 191,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,26</t>
+          <t>-100,0; 30,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 443,35</t>
+          <t>-100,0; 310,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 461,79</t>
+          <t>-17,28; 471,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 347,17</t>
+          <t>-43,5; 372,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,38; 423,68</t>
+          <t>-62,89; 504,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 231,68</t>
+          <t>-15,92; 210,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 90,28</t>
+          <t>-60,09; 83,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 220,18</t>
+          <t>-54,95; 216,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,54</t>
+          <t>0,59; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,09</t>
+          <t>0,87; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,18</t>
+          <t>-1,01; 2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,19</t>
+          <t>-0,33; 4,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,63</t>
+          <t>-1,93; 1,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,39</t>
+          <t>-2,28; 1,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,16</t>
+          <t>0,61; 3,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,48</t>
+          <t>0,18; 2,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,23</t>
+          <t>-1,16; 1,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 807,73</t>
+          <t>20,64; 760,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,97; 862,55</t>
+          <t>42,36; 813,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-96,75; 495,12</t>
+          <t>-96,58; 567,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 232,06</t>
+          <t>-13,54; 223,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 97,55</t>
+          <t>-54,69; 101,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 75,58</t>
+          <t>-68,42; 83,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,35; 259,62</t>
+          <t>23,97; 254,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 185,39</t>
+          <t>4,52; 189,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 99,42</t>
+          <t>-56,45; 87,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,95</t>
+          <t>0,22; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,04</t>
+          <t>0,36; 3,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,39</t>
+          <t>0,11; 3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,09</t>
+          <t>-1,08; 2,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,78</t>
+          <t>-1,33; 1,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,42</t>
+          <t>-0,88; 2,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,2</t>
+          <t>-0,11; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,83</t>
+          <t>-0,23; 1,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,27</t>
+          <t>0,03; 2,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 919,14</t>
+          <t>3,37; 1085,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 1074,94</t>
+          <t>-4,54; 1193,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,04; 1166,33</t>
+          <t>-3,77; 1184,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 154,51</t>
+          <t>-41,29; 175,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 145,51</t>
+          <t>-50,76; 155,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 210,55</t>
+          <t>-31,96; 195,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 229,3</t>
+          <t>-9,55; 206,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 184,91</t>
+          <t>-14,08; 162,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 228,16</t>
+          <t>-2,12; 226,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,13</t>
+          <t>-1,26; 2,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,91</t>
+          <t>-1,52; 1,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,23</t>
+          <t>-1,66; 2,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,61</t>
+          <t>-1,26; 1,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,57</t>
+          <t>-2,05; 0,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,72</t>
+          <t>0,43; 4,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,35</t>
+          <t>-0,92; 1,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,86</t>
+          <t>-1,25; 0,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,49</t>
+          <t>-0,25; 2,73</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 315,92</t>
+          <t>-54,04; 250,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 227,62</t>
+          <t>-60,73; 199,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,61; 230,4</t>
+          <t>-60,47; 220,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 225,01</t>
+          <t>-60,08; 282,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,31; 151,4</t>
+          <t>-88,99; 100,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,18; 614,64</t>
+          <t>-0,52; 694,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 144,81</t>
+          <t>-44,64; 124,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,74; 91,59</t>
+          <t>-59,26; 80,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 230,95</t>
+          <t>-14,59; 256,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,27</t>
+          <t>-2,54; 2,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,78</t>
+          <t>-3,48; 1,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,13</t>
+          <t>-3,18; 1,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,68</t>
+          <t>-2,31; 1,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,71</t>
+          <t>-1,16; 3,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,48</t>
+          <t>-0,61; 3,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,54</t>
+          <t>-2,01; 1,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,58</t>
+          <t>-1,5; 1,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,73</t>
+          <t>-1,08; 1,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 115,38</t>
+          <t>-58,96; 122,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,8; 49,97</t>
+          <t>-74,93; 55,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 58,88</t>
+          <t>-63,17; 67,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,03; 133,83</t>
+          <t>-71,29; 129,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 266,48</t>
+          <t>-39,98; 290,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 287,87</t>
+          <t>-20,78; 264,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 78,41</t>
+          <t>-54,94; 64,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,58; 85,45</t>
+          <t>-42,08; 86,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 96,51</t>
+          <t>-28,75; 87,23</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,42</t>
+          <t>-0,87; 7,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,43</t>
+          <t>-3,25; 2,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,66</t>
+          <t>-2,96; 1,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,2</t>
+          <t>-2,47; 2,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,71</t>
+          <t>-2,8; 2,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,4</t>
+          <t>-3,56; 1,41</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,47</t>
+          <t>-0,96; 3,58</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,48</t>
+          <t>-2,18; 1,4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,06</t>
+          <t>-2,57; 1,09</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 403,6</t>
+          <t>-26,84; 366,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-67,8; 161,38</t>
+          <t>-71,88; 135,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,04; 112,93</t>
+          <t>-63,12; 97,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 130,48</t>
+          <t>-63,62; 148,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-71,31; 120,62</t>
+          <t>-71,67; 147,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 65,35</t>
+          <t>-79,02; 66,77</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 175,12</t>
+          <t>-25,91; 173,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 68,89</t>
+          <t>-56,98; 69,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 46,84</t>
+          <t>-62,93; 51,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,35</t>
+          <t>-3,97; 3,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -1,02</t>
+          <t>-7,02; -0,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 1,67</t>
+          <t>-4,44; 1,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,98</t>
+          <t>-2,57; 2,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,9</t>
+          <t>-3,53; 1,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,66</t>
+          <t>-1,95; 3,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,42</t>
+          <t>-2,19; 2,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,3</t>
+          <t>-3,67; 0,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,19</t>
+          <t>-1,69; 2,21</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 208,79</t>
+          <t>-69,82; 215,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -23,0</t>
+          <t>-100,0; 19,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-70,4; 95,53</t>
+          <t>-69,26; 147,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 170,65</t>
+          <t>-53,69; 165,69</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 108,38</t>
+          <t>-72,37; 122,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 209,97</t>
+          <t>-37,48; 204,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 109,6</t>
+          <t>-47,05; 120,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-77,67; 28,41</t>
+          <t>-75,95; 26,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 106,81</t>
+          <t>-34,24; 100,25</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,9</t>
+          <t>0,3; 1,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,92</t>
+          <t>-0,42; 0,91</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,1</t>
+          <t>-0,35; 1,11</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,35</t>
+          <t>-0,07; 1,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,76</t>
+          <t>-0,67; 0,78</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,65</t>
+          <t>0,05; 1,69</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,41</t>
+          <t>0,29; 1,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,63</t>
+          <t>-0,38; 0,62</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,16</t>
+          <t>0,06; 1,2</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>11,46; 130,47</t>
+          <t>12,31; 125,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 60,72</t>
+          <t>-18,72; 61,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 74,33</t>
+          <t>-17,24; 73,09</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 71,1</t>
+          <t>-4,52; 74,72</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 39,9</t>
+          <t>-26,01; 41,09</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,17; 86,98</t>
+          <t>0,54; 87,84</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,9; 80,93</t>
+          <t>12,99; 78,01</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 36,03</t>
+          <t>-16,79; 34,41</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3,02; 65,44</t>
+          <t>2,75; 67,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,99</t>
+          <t>-1,71; 2,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,04</t>
+          <t>-2,91; 0,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,42</t>
+          <t>-1,98; 3,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,94</t>
+          <t>0,12; 4,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,06</t>
+          <t>-0,92; 2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,0</t>
+          <t>-1,01; 3,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,35</t>
+          <t>-0,26; 2,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,96</t>
+          <t>-1,31; 0,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,52</t>
+          <t>-0,98; 2,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>-1,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 191,02</t>
+          <t>-66,7; 213,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,07</t>
+          <t>-100,0; 53,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 310,54</t>
+          <t>-100,0; 353,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 471,39</t>
+          <t>-6,78; 545,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 372,66</t>
+          <t>-47,62; 331,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 504,79</t>
+          <t>-51,53; 460,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 210,74</t>
+          <t>-15,36; 204,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 83,55</t>
+          <t>-57,38; 86,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 216,42</t>
+          <t>-52,73; 199,02</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,61</t>
+          <t>0,62; 3,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,06</t>
+          <t>0,82; 4,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,44</t>
+          <t>-0,8; 2,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,2</t>
+          <t>-0,33; 4,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,83</t>
+          <t>-1,95; 1,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,47</t>
+          <t>-2,1; 1,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,32</t>
+          <t>0,65; 3,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,38</t>
+          <t>-0,02; 2,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,15</t>
+          <t>-0,92; 1,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,47%</t>
+          <t>-4,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-5,46%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 760,67</t>
+          <t>25,7; 744,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,36; 813,87</t>
+          <t>43,94; 993,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-96,58; 567,89</t>
+          <t>-100,0; 852,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 223,85</t>
+          <t>-11,83; 242,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,69; 101,04</t>
+          <t>-53,51; 108,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 83,6</t>
+          <t>-61,2; 110,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,97; 254,6</t>
+          <t>26,74; 264,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 189,27</t>
+          <t>-4,02; 186,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 87,27</t>
+          <t>-45,59; 132,55</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,22 +1081,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0,77</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,93</t>
+          <t>0,35; 3,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,01</t>
+          <t>0,22; 2,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,39</t>
+          <t>0,1; 3,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,26</t>
+          <t>-1,13; 2,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,76</t>
+          <t>-1,5; 1,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,57</t>
+          <t>-0,92; 2,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,13</t>
+          <t>-0,04; 2,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,76</t>
+          <t>-0,21; 1,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,31</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>216,59%</t>
+          <t>178,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 1085,73</t>
+          <t>-2,35; 861,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1193,01</t>
+          <t>-6,0; 844,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1184,63</t>
+          <t>-9,74; 922,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 175,36</t>
+          <t>-43,19; 169,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 155,53</t>
+          <t>-55,79; 131,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 195,23</t>
+          <t>-33,79; 190,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 206,17</t>
+          <t>-5,18; 217,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 162,2</t>
+          <t>-14,13; 203,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 226,79</t>
+          <t>-2,95; 207,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,0</t>
+          <t>-1,49; 2,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,72</t>
+          <t>-1,4; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,29</t>
+          <t>-0,43; 3,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,62</t>
+          <t>-1,3; 1,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,45</t>
+          <t>-1,94; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,5</t>
+          <t>0,08; 2,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,28</t>
+          <t>-0,81; 1,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,81</t>
+          <t>-1,09; 0,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,73</t>
+          <t>0,3; 2,73</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>148,7%</t>
+          <t>108,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,04; 250,24</t>
+          <t>-65,98; 241,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,73; 199,12</t>
+          <t>-60,5; 244,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,47; 220,15</t>
+          <t>-26,04; 402,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 282,89</t>
+          <t>-62,7; 248,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,99; 100,59</t>
+          <t>-88,11; 87,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 694,72</t>
+          <t>-5,18; 441,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 124,33</t>
+          <t>-40,48; 165,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 80,41</t>
+          <t>-55,28; 93,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 256,5</t>
+          <t>6,63; 270,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,33</t>
+          <t>-2,63; 2,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,05</t>
+          <t>-3,51; 1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,13</t>
+          <t>-3,17; 0,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,56</t>
+          <t>-2,29; 1,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,74</t>
+          <t>-0,94; 3,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,25</t>
+          <t>-0,17; 3,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,17</t>
+          <t>-2,01; 1,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,62</t>
+          <t>-1,77; 1,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,8</t>
+          <t>-1,0; 1,91</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-23,99%</t>
+          <t>-25,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 122,89</t>
+          <t>-61,73; 119,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,93; 55,6</t>
+          <t>-75,06; 54,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 67,88</t>
+          <t>-66,29; 48,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 129,56</t>
+          <t>-69,85; 146,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 290,82</t>
+          <t>-33,43; 290,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 264,88</t>
+          <t>-11,05; 337,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 64,5</t>
+          <t>-56,11; 65,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 86,47</t>
+          <t>-47,82; 75,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 87,23</t>
+          <t>-26,48; 103,35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 7,16</t>
+          <t>-0,92; 6,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,32</t>
+          <t>-3,09; 2,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,59</t>
+          <t>-3,21; 1,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,35</t>
+          <t>-2,78; 2,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,09</t>
+          <t>-3,13; 1,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,41</t>
+          <t>-1,71; 2,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,58</t>
+          <t>-1,25; 3,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,4</t>
+          <t>-2,3; 1,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,09</t>
+          <t>-1,63; 1,44</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-15,79%</t>
+          <t>-17,82%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-21,2%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-19,5%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 366,22</t>
+          <t>-33,61; 335,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 135,64</t>
+          <t>-70,19; 129,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 97,62</t>
+          <t>-67,48; 95,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,62; 148,73</t>
+          <t>-67,4; 166,24</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-71,67; 147,39</t>
+          <t>-76,19; 102,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,02; 66,77</t>
+          <t>-41,41; 143,3</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 173,9</t>
+          <t>-34,37; 147,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 69,04</t>
+          <t>-59,03; 66,26</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-62,93; 51,55</t>
+          <t>-40,64; 67,82</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,88</t>
+          <t>-4,06; 3,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -0,84</t>
+          <t>-6,81; -0,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,99</t>
+          <t>-4,75; 1,88</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,92</t>
+          <t>-2,47; 2,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,77</t>
+          <t>-3,56; 1,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,55</t>
+          <t>-1,49; 3,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,58</t>
+          <t>-2,05; 2,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,43</t>
+          <t>-3,79; 0,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,21</t>
+          <t>-1,63; 2,41</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-24,8%</t>
+          <t>-23,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-69,82; 215,71</t>
+          <t>-69,98; 205,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,13</t>
+          <t>-100,0; -0,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,26; 147,89</t>
+          <t>-71,83; 114,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-53,69; 165,69</t>
+          <t>-53,89; 171,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,37; 122,0</t>
+          <t>-72,41; 105,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 204,98</t>
+          <t>-33,07; 218,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 120,61</t>
+          <t>-46,5; 120,55</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,95; 26,53</t>
+          <t>-77,74; 29,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 100,25</t>
+          <t>-33,75; 114,14</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>0,14</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,87</t>
+          <t>0,3; 1,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,91</t>
+          <t>-0,4; 0,92</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,11</t>
+          <t>-0,17; 1,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,48</t>
+          <t>-0,06; 1,47</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,78</t>
+          <t>-0,74; 0,81</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,69</t>
+          <t>0,41; 1,82</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,36</t>
+          <t>0,31; 1,44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,62</t>
+          <t>-0,37; 0,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,2</t>
+          <t>0,29; 1,31</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12,31; 125,44</t>
+          <t>13,66; 117,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 61,01</t>
+          <t>-19,8; 61,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 73,09</t>
+          <t>-8,61; 86,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 74,72</t>
+          <t>-2,11; 81,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 41,09</t>
+          <t>-28,23; 42,96</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,54; 87,84</t>
+          <t>12,82; 101,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,99; 78,01</t>
+          <t>13,56; 81,36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 34,41</t>
+          <t>-16,44; 36,41</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2,75; 67,66</t>
+          <t>13,0; 73,98</t>
         </is>
       </c>
     </row>
